--- a/data/processed/harmonization/Physical__Dry_bulk_density/dois_filtering.xlsx
+++ b/data/processed/harmonization/Physical__Dry_bulk_density/dois_filtering.xlsx
@@ -1332,7 +1332,7 @@
         <v>60</v>
       </c>
       <c r="D28">
-        <v>539</v>
+        <v>597</v>
       </c>
       <c r="E28" t="s">
         <v>99</v>
@@ -1352,7 +1352,7 @@
         <v>60</v>
       </c>
       <c r="D29">
-        <v>539</v>
+        <v>597</v>
       </c>
       <c r="E29" t="s">
         <v>100</v>
